--- a/docs/template-report.xlsx
+++ b/docs/template-report.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -485,14 +485,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Шаблон отчёта ВТБ «Аналитика портфеля», версия 1</t>
+          <t>Шаблон отчёта ВТБ «Аналитика портфеля», версия 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполните листы «Отчёт», «Позиции», «Купоны» по PDF-отчёту и загрузите файл в кабинете. Формат только .xlsx.</t>
+          <t>Заполните листы «Отчёт», «Позиции», «Купоны» по PDF-отчёту ВТБ за один календарный месяц и загрузите файл в кабинете. Формат только .xlsx.</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3. Даты — настоящие даты (формат ДД.ММ.ГГГГ).</t>
+          <t>3. Даты — настоящие даты (формат ДД.ММ.ГГГГ). Период «с» и «по» должен лежать в одном месяце, как в отчёте за месяц (01.09–30.09). Отчёт за несколько месяцев приложение не примет.</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>9. Жёлтые ячейки — для ввода.</t>
+          <t>9. Если в отчёте нет раздела (например, «Полученные выплаты» или «Облигации»), оставьте лист пустым и поставьте 0 в «Итого». Порядок разделов в PDF может быть любым.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10. Жёлтые ячейки — для ввода.</t>
         </is>
       </c>
     </row>
@@ -580,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -612,7 +619,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -623,165 +630,152 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Дата отчёта</t>
+          <t>Период с</t>
         </is>
       </c>
       <c r="B3" s="8" t="n"/>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Из шапки: «Дата отчёта».</t>
+          <t>Из шапки: «За период …» (первая дата). Период должен быть одним календарным месяцем.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Период с</t>
+          <t>Период по</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Из шапки: «За период …» (первая дата).</t>
+          <t>Из шапки: «За период …» (вторая дата). Это дата снимка. «Дату отчёта» из шапки не переносить.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Период по</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
+          <t>Стоимость портфеля, ₽</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Из шапки: «За период …» (вторая дата).</t>
+          <t>Из шапки: «Стоимость».</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Стоимость портфеля, ₽</t>
+          <t>Деньги, ₽</t>
         </is>
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Из шапки: «Стоимость».</t>
+          <t>Раздел «Деньги», строка «Рубль РФ», колонка «Сумма».</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Деньги, ₽</t>
+          <t>Пополнения за период, ₽</t>
         </is>
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Раздел «Деньги», строка «Рубль РФ», колонка «Сумма».</t>
+          <t>«Пополнения и выводы», строка «Рубль РФ», колонка «Пополнение». Без знака «+». Если «-», писать 0.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Пополнения за период, ₽</t>
+          <t>Выводы за период, ₽</t>
         </is>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>«Пополнения и выводы», строка «Рубль РФ», колонка «Пополнение». Без знака «+». Если «-», писать 0.</t>
+          <t>Та же таблица, колонка «Вывод». Если «-», писать 0.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Выводы за период, ₽</t>
+          <t>Выплаты на счёт в банке, ₽</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Та же таблица, колонка «Вывод». Если «-», писать 0.</t>
+          <t>Та же таблица, колонка «Выплаты на счёт в банке». Если «-», писать 0.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Выплаты на счёт в банке, ₽</t>
+          <t>Комиссии, ₽</t>
         </is>
       </c>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Та же таблица, колонка «Выплаты на счёт в банке». Если «-», писать 0.</t>
+          <t>«Комиссии и налоги»: брокерская + биржевая + маржинальное кредитование + прочие услуги. Без знака «−».</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Комиссии, ₽</t>
+          <t>Налоги, ₽</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>«Комиссии и налоги»: брокерская + биржевая + маржинальное кредитование + прочие услуги. Без знака «−».</t>
+          <t>«Комиссии и налоги», колонка «Налоги». Без знака «−». Если «-», писать 0.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Налоги, ₽</t>
+          <t>Итого по облигациям, ₽</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>«Комиссии и налоги», колонка «Налоги». Без знака «−». Если «-», писать 0.</t>
+          <t>Строка «Итого» в таблице «Облигации». Нет раздела — 0.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Итого по облигациям, ₽</t>
+          <t>Итого по фондам, ₽</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Строка «Итого» в таблице «Облигации». Нет раздела — 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Итого по фондам, ₽</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
           <t>Строка «Итого» в таблице «Фонды». Нет раздела — 0.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B3:B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Дата" error="Введите дату ДД.ММ.ГГГГ" type="date" operator="greaterThan">
+    <dataValidation sqref="B2:B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Дата" error="Введите дату ДД.ММ.ГГГГ" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:B14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Сумма" error="Нужно число 0 или больше, без знака минус и без текста" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B4:B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Сумма" error="Нужно число 0 или больше, без знака минус и без текста" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
